--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_14_AI Evaluation _ Benchmarking/Day_14_Phan_01_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_14_AI Evaluation _ Benchmarking/Day_14_Phan_01_19_Cau.xlsx
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1065,7 +1065,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Precision=Recall=3/4 nên F1=2PR/(P+R)=0,75.</t>
+          <t>Token F1: Multiset overlap = 3 tokens; candidate = 4 tokens, reference = 4 tokens. Precision = 3/4, Recall = 3/4 =&gt; F1 = 2 * (3/4 * 3/4) / (3/4 + 3/4) = 0,75.</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1265,7 +1265,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mẫu số là số từ của reference.</t>
+          <t>Word Error Rate (WER) = (S + D + I) / N_ref = (1 + 0 + 1) / 4 = 2 / 4 = 0,5.</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.708</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1463,7 +1463,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính precision tại từng rank relevant, lấy AP từng query rồi mới lấy mean.</t>
+          <t>Mean Average Precision (MAP): Query 1 relevant tại rank 1 và 3 =&gt; AP1 = (1/1 + 2/3) / 2 = (5/3) / 2 = 5/6 ≈ 0,8333. Query 2 relevant tại rank 2 và 3 =&gt; AP2 = (1/2 + 2/3) / 2 = (7/6) / 2 = 7/12 ≈ 0,5833. MAP = (5/6 + 7/12) / 2 = 17 / 24 ≈ 0,7083, làm tròn 3 chữ số là 0,708.</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
@@ -1518,7 +1518,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Thành phần nào không phụ thuộc detector hiện có?</t>
+          <t>Mẫu lấy vết (mixed trace sample) để vừa tìm lỗi chưa biết vừa phủ rủi ro đã biết gồm: (a) Lưu lượng ngẫu nhiên theo tỷ lệ cố định (để phát hiện lỗi chưa biết), (b) đại diện các nhóm truy vấn phổ biến, (c) các trường hợp bất thường và cờ cảnh báo tự động, (d) phản hồi tiêu cực từ người dùng.</t>
         </is>
       </c>
     </row>
